--- a/fliad-plugin/plugin-dahua/src/main/resources/_vfs/nop/excel/imp/dahua.template.xlsx
+++ b/fliad-plugin/plugin-dahua/src/main/resources/_vfs/nop/excel/imp/dahua.template.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\can\entropy-cloud\nop-ooxml\nop-ooxml-xlsx\src\test\resources\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IdeaProjects\fliad-viid\fliad-plugin\plugin-dahua\src\main\resources\_vfs\nop\excel\imp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{31B5068F-1ECE-48E5-AAA3-DA947245C0F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B246DEE-EE39-4AC1-A038-73C767F338C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{392982CA-C4D8-434C-9678-96E43A892558}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{392982CA-C4D8-434C-9678-96E43A892558}"/>
   </bookViews>
   <sheets>
-    <sheet name="海康设备" sheetId="1" r:id="rId4"/>
+    <sheet name="海康设备" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,41 +25,80 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>nop</author>
-  </authors>
-  <commentList/>
-</comments>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>设备编号</t>
+  </si>
+  <si>
+    <t>设备名称</t>
+  </si>
+  <si>
+    <t>IP地址</t>
+  </si>
+  <si>
+    <t>端口</t>
+  </si>
+  <si>
+    <t>用户名</t>
+  </si>
+  <si>
+    <t>密码</t>
+  </si>
+  <si>
+    <t>启用状态</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>主键</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
-      <sz val="11"/>
+      <family val="2"/>
       <charset val="134"/>
-      <family val="2"/>
-      <color rgb="000000"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
       <family val="2"/>
-      <color rgb="FFFFFF"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -68,104 +107,102 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="44749F"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="BDD6EE"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="E2EEDA"/>
+        <fgColor rgb="FF44749F"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="4">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0">
-      <alignment vertical="center" horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0">
-      <alignment vertical="center" horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0">
-      <alignment vertical="center" horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0">
-      <alignment vertical="center" horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0">
-      <alignment vertical="center" horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="HyperLink" xfId="0" builtinId="8"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -467,71 +504,62 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{a7e86b44-d99c-406b-b87e-dc5d0d7e3f43}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.0" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7E86B44-D99C-406B-B87E-DC5D0D7E3F43}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>设备编号</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>设备名称</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>IP地址</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>端口</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>用户名</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>密码</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>启用状态</t>
-        </is>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"1-启用,0-禁用"</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>